--- a/data_assets/mapping/ods_to_dwd/DWD明细层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/ods_to_dwd/DWD明细层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9060" firstSheet="11" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="客户基本信息" sheetId="1" r:id="rId1"/>
@@ -23,10 +23,10 @@
     <sheet name="机构表" sheetId="12" r:id="rId14"/>
     <sheet name="货币汇率表" sheetId="13" r:id="rId15"/>
     <sheet name="客户KYC信息表" sheetId="14" r:id="rId16"/>
-    <sheet name="逻辑模型维度描述" sheetId="15" state="hidden" r:id="rId17"/>
+    <sheet name="睡眠户信息表" sheetId="19" r:id="rId17"/>
+    <sheet name="逻辑模型维度描述" sheetId="15" state="hidden" r:id="rId18"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId18"/>
     <externalReference r:id="rId19"/>
     <externalReference r:id="rId20"/>
     <externalReference r:id="rId21"/>
@@ -89,6 +89,17 @@
     <definedName name="_Toc205004289" localSheetId="2">#REF!</definedName>
     <definedName name="_Toc275247984" localSheetId="2">#REF!</definedName>
     <definedName name="Basel" localSheetId="2">[2]Parameters!$C$32:$C$33</definedName>
+    <definedName name="Database" localSheetId="16" hidden="1">#REF!</definedName>
+    <definedName name="_Toc205004290" localSheetId="16">#REF!</definedName>
+    <definedName name="常用数据标准" localSheetId="16">#REF!</definedName>
+    <definedName name="_Toc205004288" localSheetId="16">#REF!</definedName>
+    <definedName name="_Toc256075879" localSheetId="16">#REF!</definedName>
+    <definedName name="YesNoBasel2" localSheetId="16">[3]Parameters!#REF!</definedName>
+    <definedName name="area" localSheetId="16">[1]建议意见清单!$A$1:$F$21</definedName>
+    <definedName name="_Toc205004291" localSheetId="16">#REF!</definedName>
+    <definedName name="_Toc205004289" localSheetId="16">#REF!</definedName>
+    <definedName name="_Toc275247984" localSheetId="16">#REF!</definedName>
+    <definedName name="Basel" localSheetId="16">[2]Parameters!$C$32:$C$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -108,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2769" uniqueCount="902">
   <si>
     <t>返回目录</t>
   </si>
@@ -1348,6 +1359,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>WHERE T1.CHONGZBZ = '0' --</t>
     </r>
     <r>
@@ -2914,6 +2932,18 @@
   </si>
   <si>
     <t>可用额度</t>
+  </si>
+  <si>
+    <t>睡眠户信息表</t>
+  </si>
+  <si>
+    <t>DWD_CUST_DORMANT_ACCOUT</t>
+  </si>
+  <si>
+    <t>DATA_DATE</t>
+  </si>
+  <si>
+    <t>数据日期</t>
   </si>
   <si>
     <t>主题</t>
@@ -5914,31 +5944,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="实体清单"/>
-      <sheetName val="客户基本信息表"/>
-      <sheetName val="客户关联关系表"/>
-      <sheetName val="家庭成员信息"/>
-      <sheetName val="存款账户信息表"/>
-      <sheetName val="资产交易信息表"/>
-      <sheetName val="逻辑模型维度描述"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -14335,6 +14340,448 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q68"/>
+  <sheetFormatPr defaultColWidth="8.23148148148148" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="2" max="2" width="27.5462962962963" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="4" max="4" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="5" max="5" width="18.6666666666667" style="6" customWidth="1"/>
+    <col min="6" max="6" width="10.7685185185185" style="6" customWidth="1"/>
+    <col min="7" max="7" width="12.1018518518519" style="6" customWidth="1"/>
+    <col min="8" max="8" width="8.76851851851852" style="6" customWidth="1"/>
+    <col min="9" max="9" width="8.23148148148148" style="6" customWidth="1"/>
+    <col min="10" max="10" width="8.76851851851852" style="6" customWidth="1"/>
+    <col min="11" max="11" width="8.23148148148148" style="6" customWidth="1"/>
+    <col min="12" max="12" width="24.1851851851852" style="6" customWidth="1"/>
+    <col min="13" max="13" width="23" style="6" customWidth="1"/>
+    <col min="14" max="14" width="17.3611111111111" style="6" customWidth="1"/>
+    <col min="15" max="15" width="16.8796296296296" style="6" customWidth="1"/>
+    <col min="16" max="16" width="10.2685185185185" style="6" customWidth="1"/>
+    <col min="17" max="17" width="16.8148148148148" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" s="3" customFormat="1" ht="21" customHeight="1" spans="1:17">
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="30.6" customHeight="1" spans="1:17">
+      <c r="B3" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="17.55" customHeight="1" spans="1:17">
+      <c r="B4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="13"/>
+      <c r="L4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="18"/>
+    </row>
+    <row r="5" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
+      <c r="B5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25" t="s">
+        <v>876</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="D6" s="26">
+        <v>8</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>877</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+    </row>
+    <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="D7" s="26">
+        <v>20</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="26"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+    </row>
+    <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+    </row>
+    <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+    </row>
+    <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B11" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="13"/>
+      <c r="L11" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B12" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="13"/>
+      <c r="L12" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="M12" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="O12" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="P12" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="13" s="4" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="13"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="18"/>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:17">
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="18"/>
+    </row>
+    <row r="15" s="4" customFormat="1" spans="1:17">
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="18"/>
+    </row>
+    <row r="16" ht="13.95" customHeight="1" spans="1:17">
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="18"/>
+    </row>
+    <row r="17" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L17" s="45"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="18"/>
+    </row>
+    <row r="18" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L18" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="18"/>
+    </row>
+    <row r="19" ht="56" customHeight="1" spans="12:17">
+      <c r="L19" s="48"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="18"/>
+    </row>
+    <row r="20" ht="13.95" customHeight="1"/>
+    <row r="21" ht="13.95" customHeight="1"/>
+    <row r="22" ht="13.95" customHeight="1"/>
+    <row r="23" ht="13.95" customHeight="1"/>
+    <row r="24" ht="13.95" customHeight="1"/>
+    <row r="25" ht="13.95" customHeight="1"/>
+    <row r="26" ht="13.95" customHeight="1"/>
+    <row r="27" ht="13.95" customHeight="1"/>
+    <row r="28" ht="13.95" customHeight="1"/>
+    <row r="29" ht="13.95" customHeight="1"/>
+    <row r="30" ht="13.95" customHeight="1"/>
+    <row r="31" ht="13.95" customHeight="1"/>
+    <row r="32" ht="13.95" customHeight="1"/>
+    <row r="33" ht="13.95" customHeight="1"/>
+    <row r="34" ht="13.95" customHeight="1"/>
+    <row r="35" ht="13.95" customHeight="1"/>
+    <row r="36" ht="13.95" customHeight="1"/>
+    <row r="37" ht="13.95" customHeight="1"/>
+    <row r="38" ht="13.95" customHeight="1"/>
+    <row r="39" ht="13.95" customHeight="1"/>
+    <row r="40" ht="13.95" customHeight="1"/>
+    <row r="41" ht="13.95" customHeight="1"/>
+    <row r="42" ht="13.95" customHeight="1"/>
+    <row r="43" ht="13.95" customHeight="1"/>
+    <row r="44" ht="13.95" customHeight="1"/>
+    <row r="45" ht="13.95" customHeight="1"/>
+    <row r="46" ht="13.95" customHeight="1"/>
+    <row r="47" ht="13.95" customHeight="1"/>
+    <row r="48" ht="13.95" customHeight="1"/>
+    <row r="49" ht="13.95" customHeight="1"/>
+    <row r="50" ht="13.95" customHeight="1"/>
+    <row r="51" ht="13.95" customHeight="1"/>
+    <row r="52" ht="13.95" customHeight="1"/>
+    <row r="53" ht="13.95" customHeight="1"/>
+    <row r="54" ht="13.95" customHeight="1"/>
+    <row r="55" ht="13.95" customHeight="1"/>
+    <row r="56" ht="13.95" customHeight="1"/>
+    <row r="57" ht="13.95" customHeight="1"/>
+    <row r="58" ht="13.95" customHeight="1"/>
+    <row r="59" ht="13.95" customHeight="1"/>
+    <row r="60" ht="13.95" customHeight="1"/>
+    <row r="61" ht="13.95" customHeight="1"/>
+    <row r="62" ht="13.95" customHeight="1"/>
+    <row r="63" ht="13.95" customHeight="1"/>
+    <row r="64" ht="13.95" customHeight="1"/>
+    <row r="65" ht="13.95" customHeight="1"/>
+    <row r="66" ht="13.95" customHeight="1"/>
+    <row r="67" ht="13.95" customHeight="1"/>
+    <row r="68" ht="13.95" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="L11:Q11"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="L19:Q19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet690"/>
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
@@ -14347,39 +14794,39 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -14388,61 +14835,61 @@
         <v>307</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -14450,7 +14897,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -14458,7 +14905,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>

--- a/data_assets/mapping/ods_to_dwd/DWD明细层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/ods_to_dwd/DWD明细层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" firstSheet="6" activeTab="8"/>
+    <workbookView windowWidth="22188" windowHeight="9060" firstSheet="3" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="客户基本信息" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="936">
   <si>
     <t>返回目录</t>
   </si>
@@ -2032,6 +2032,12 @@
   </si>
   <si>
     <t>PROD_RISK_LEVEL</t>
+  </si>
+  <si>
+    <t>CFM_AMT</t>
+  </si>
+  <si>
+    <t>确认金额</t>
   </si>
   <si>
     <t xml:space="preserve">T1_CUST_INFO </t>
@@ -8048,12 +8054,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -8157,13 +8163,13 @@
       <c r="I6" s="90"/>
       <c r="J6" s="90"/>
       <c r="L6" s="32" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="O6" s="34"/>
       <c r="P6" s="32"/>
@@ -8172,14 +8178,14 @@
     <row r="7" s="86" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="32" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C7" s="88"/>
       <c r="D7" s="32" t="s">
         <v>272</v>
       </c>
       <c r="E7" s="84" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -8187,13 +8193,13 @@
       <c r="I7" s="90"/>
       <c r="J7" s="90"/>
       <c r="L7" s="32" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O7" s="34"/>
       <c r="P7" s="32"/>
@@ -8202,14 +8208,14 @@
     <row r="8" s="86" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="32" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C8" s="88"/>
       <c r="D8" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="84" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -8217,13 +8223,13 @@
       <c r="I8" s="90"/>
       <c r="J8" s="90"/>
       <c r="L8" s="32" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="O8" s="34"/>
       <c r="P8" s="32"/>
@@ -8232,14 +8238,14 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="87"/>
       <c r="B9" s="32" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C9" s="82"/>
       <c r="D9" s="32" t="s">
         <v>40</v>
       </c>
       <c r="E9" s="84" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -8247,13 +8253,13 @@
       <c r="I9" s="42"/>
       <c r="J9" s="91"/>
       <c r="L9" s="32" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="O9" s="34"/>
       <c r="P9" s="32"/>
@@ -8269,7 +8275,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="84" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -8277,13 +8283,13 @@
       <c r="I10" s="42"/>
       <c r="J10" s="91"/>
       <c r="L10" s="32" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N10" s="32" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="O10" s="34"/>
       <c r="P10" s="32"/>
@@ -8292,14 +8298,14 @@
     <row r="11" s="86" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="32" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C11" s="88"/>
       <c r="D11" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="84" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -8307,13 +8313,13 @@
       <c r="I11" s="90"/>
       <c r="J11" s="90"/>
       <c r="L11" s="32" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N11" s="32" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O11" s="34"/>
       <c r="P11" s="32"/>
@@ -8322,14 +8328,14 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="32" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C12" s="82"/>
       <c r="D12" s="32" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="84" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -8337,13 +8343,13 @@
       <c r="I12" s="53"/>
       <c r="J12" s="42"/>
       <c r="L12" s="32" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N12" s="32" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O12" s="34"/>
       <c r="P12" s="32"/>
@@ -8352,14 +8358,14 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="87"/>
       <c r="B13" s="32" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C13" s="82"/>
       <c r="D13" s="32" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="84" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -8367,13 +8373,13 @@
       <c r="I13" s="53"/>
       <c r="J13" s="42"/>
       <c r="L13" s="32" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N13" s="32" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="O13" s="34"/>
       <c r="P13" s="32"/>
@@ -8503,13 +8509,13 @@
       <c r="I19" s="11"/>
       <c r="J19" s="13"/>
       <c r="L19" s="32" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M19" s="32" t="s">
         <v>153</v>
       </c>
       <c r="N19" s="33" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="O19" s="34"/>
       <c r="P19" s="43"/>
@@ -8517,37 +8523,37 @@
     </row>
     <row r="20" s="4" customFormat="1" spans="2:17">
       <c r="L20" s="32" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M20" s="32" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="O20" s="34" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="P20" s="43" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="Q20" s="18"/>
     </row>
     <row r="21" s="4" customFormat="1" spans="2:17">
       <c r="L21" s="32" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M21" s="32" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O21" s="34" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P21" s="43" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="Q21" s="18"/>
     </row>
@@ -8753,12 +8759,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -8898,7 +8904,7 @@
         <v>544</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="O7" s="33" t="s">
         <v>29</v>
@@ -8909,14 +8915,14 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="50"/>
       <c r="B8" s="33" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>272</v>
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="34" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F8" s="51"/>
       <c r="G8" s="51"/>
@@ -8924,16 +8930,16 @@
       <c r="I8" s="53"/>
       <c r="J8" s="42"/>
       <c r="L8" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M8" s="33" t="s">
         <v>547</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="O8" s="33" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="P8" s="54"/>
       <c r="Q8" s="54"/>
@@ -8941,14 +8947,14 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="50"/>
       <c r="B9" s="33" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="34" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -8965,14 +8971,14 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="50"/>
       <c r="B10" s="33" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>329</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="34" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -8980,16 +8986,16 @@
       <c r="I10" s="53"/>
       <c r="J10" s="42"/>
       <c r="L10" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M10" s="33" t="s">
         <v>547</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="O10" s="33" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="P10" s="54"/>
       <c r="Q10" s="54"/>
@@ -9012,7 +9018,7 @@
       <c r="I11" s="53"/>
       <c r="J11" s="42"/>
       <c r="L11" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M11" s="33" t="s">
         <v>547</v>
@@ -9044,7 +9050,7 @@
       <c r="I12" s="53"/>
       <c r="J12" s="42"/>
       <c r="L12" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M12" s="33" t="s">
         <v>547</v>
@@ -9061,14 +9067,14 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="50"/>
       <c r="B13" s="33" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="34" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="51"/>
@@ -9076,16 +9082,16 @@
       <c r="I13" s="53"/>
       <c r="J13" s="42"/>
       <c r="L13" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M13" s="33" t="s">
         <v>547</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="O13" s="81" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="P13" s="54"/>
       <c r="Q13" s="54"/>
@@ -9402,19 +9408,19 @@
     </row>
     <row r="30" s="4" customFormat="1" spans="1:17">
       <c r="L30" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M30" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N30" s="66" t="s">
         <v>547</v>
       </c>
       <c r="O30" s="66" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="P30" s="43" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="Q30" s="18"/>
     </row>
@@ -9630,12 +9636,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -9769,16 +9775,16 @@
       <c r="I7" s="53"/>
       <c r="J7" s="42"/>
       <c r="L7" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="P7" s="54"/>
       <c r="Q7" s="54"/>
@@ -9786,10 +9792,10 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="50"/>
       <c r="B8" s="33" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="59" t="s">
@@ -9810,14 +9816,14 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="50"/>
       <c r="B9" s="33" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="59" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -9825,16 +9831,16 @@
       <c r="I9" s="53"/>
       <c r="J9" s="42"/>
       <c r="L9" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="O9" s="33" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="P9" s="54"/>
       <c r="Q9" s="54"/>
@@ -9842,14 +9848,14 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="50"/>
       <c r="B10" s="58" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="59" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -9857,13 +9863,13 @@
       <c r="I10" s="53"/>
       <c r="J10" s="42"/>
       <c r="L10" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="O10" s="33" t="s">
         <v>404</v>
@@ -9877,7 +9883,7 @@
         <v>517</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="59" t="s">
@@ -9889,13 +9895,13 @@
       <c r="I11" s="53"/>
       <c r="J11" s="42"/>
       <c r="L11" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="O11" s="33" t="s">
         <v>518</v>
@@ -9921,10 +9927,10 @@
       <c r="I12" s="53"/>
       <c r="J12" s="42"/>
       <c r="L12" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N12" s="33" t="s">
         <v>509</v>
@@ -9953,13 +9959,13 @@
       <c r="I13" s="53"/>
       <c r="J13" s="42"/>
       <c r="L13" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="O13" s="33" t="s">
         <v>325</v>
@@ -10002,14 +10008,14 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="50"/>
       <c r="B15" s="33" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>329</v>
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="59" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="51"/>
@@ -10017,16 +10023,16 @@
       <c r="I15" s="53"/>
       <c r="J15" s="42"/>
       <c r="L15" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M15" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="O15" s="33" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="P15" s="54"/>
       <c r="Q15" s="54"/>
@@ -10049,10 +10055,10 @@
       <c r="I16" s="53"/>
       <c r="J16" s="42"/>
       <c r="L16" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N16" s="33" t="s">
         <v>478</v>
@@ -10081,10 +10087,10 @@
       <c r="I17" s="53"/>
       <c r="J17" s="42"/>
       <c r="L17" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M17" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N17" s="33" t="s">
         <v>486</v>
@@ -10113,16 +10119,16 @@
       <c r="I18" s="53"/>
       <c r="J18" s="42"/>
       <c r="L18" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M18" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="O18" s="33" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="P18" s="54"/>
       <c r="Q18" s="54"/>
@@ -10145,16 +10151,16 @@
       <c r="I19" s="53"/>
       <c r="J19" s="42"/>
       <c r="L19" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M19" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N19" s="33" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="O19" s="33" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="P19" s="54"/>
       <c r="Q19" s="54"/>
@@ -10176,10 +10182,10 @@
       <c r="I20" s="53"/>
       <c r="J20" s="42"/>
       <c r="L20" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M20" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N20" s="33"/>
       <c r="O20" s="33"/>
@@ -10188,30 +10194,30 @@
     </row>
     <row r="21" s="5" customFormat="1" ht="32.4" spans="1:17">
       <c r="B21" s="25" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>181</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="27" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="I21" s="53"/>
       <c r="J21" s="42"/>
       <c r="L21" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N21" s="64" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="O21" s="64" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="P21" s="65"/>
       <c r="Q21" s="46"/>
@@ -10232,13 +10238,13 @@
       <c r="I22" s="53"/>
       <c r="J22" s="42"/>
       <c r="L22" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M22" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N22" s="64" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O22" s="27" t="s">
         <v>23</v>
@@ -10262,13 +10268,13 @@
       <c r="I23" s="53"/>
       <c r="J23" s="42"/>
       <c r="L23" s="33" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M23" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N23" s="64" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="O23" s="64" t="s">
         <v>314</v>
@@ -10298,7 +10304,7 @@
         <v>522</v>
       </c>
       <c r="N24" s="64" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="O24" s="64" t="s">
         <v>385</v>
@@ -10422,16 +10428,16 @@
         <v>460</v>
       </c>
       <c r="M30" s="33" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N30" s="66" t="s">
         <v>547</v>
       </c>
       <c r="O30" s="66" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="P30" s="43" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="Q30" s="18"/>
     </row>
@@ -10647,12 +10653,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -10754,16 +10760,16 @@
       <c r="I6" s="53"/>
       <c r="J6" s="42"/>
       <c r="L6" s="33" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N6" s="33" t="s">
         <v>545</v>
       </c>
       <c r="O6" s="57" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="P6" s="54"/>
       <c r="Q6" s="54"/>
@@ -10771,14 +10777,14 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="50"/>
       <c r="B7" s="33" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="34" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="F7" s="51"/>
       <c r="G7" s="51"/>
@@ -10795,14 +10801,14 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="50"/>
       <c r="B8" s="33" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="34" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="F8" s="51"/>
       <c r="G8" s="51"/>
@@ -10810,13 +10816,13 @@
       <c r="I8" s="53"/>
       <c r="J8" s="42"/>
       <c r="L8" s="33" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="O8" s="33"/>
       <c r="P8" s="54"/>
@@ -10825,14 +10831,14 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="50"/>
       <c r="B9" s="33" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="34" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -10840,22 +10846,22 @@
       <c r="I9" s="53"/>
       <c r="J9" s="42"/>
       <c r="L9" s="33" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M9" s="33" t="s">
         <v>25</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="O9" s="33" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="P9" s="54" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="Q9" s="54" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
@@ -10868,7 +10874,7 @@
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="34" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -10876,16 +10882,16 @@
       <c r="I10" s="53"/>
       <c r="J10" s="42"/>
       <c r="L10" s="33" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="O10" s="33" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="P10" s="54"/>
       <c r="Q10" s="54"/>
@@ -10893,14 +10899,14 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="50"/>
       <c r="B11" s="33" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="34" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
@@ -10908,16 +10914,16 @@
       <c r="I11" s="53"/>
       <c r="J11" s="42"/>
       <c r="L11" s="33" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="O11" s="57" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="P11" s="54"/>
       <c r="Q11" s="54"/>
@@ -10940,16 +10946,16 @@
       <c r="I12" s="53"/>
       <c r="J12" s="42"/>
       <c r="L12" s="33" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="O12" s="57" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="P12" s="54"/>
       <c r="Q12" s="54"/>
@@ -11172,12 +11178,12 @@
         <v>1</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
@@ -11308,14 +11314,14 @@
     <row r="35" ht="13.95" customHeight="1" spans="1:17">
       <c r="A35" s="50"/>
       <c r="B35" s="33" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C35" s="33" t="s">
         <v>32</v>
       </c>
       <c r="D35" s="32"/>
       <c r="E35" s="34" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="F35" s="51"/>
       <c r="G35" s="51"/>
@@ -11333,14 +11339,14 @@
     <row r="36" ht="13.95" customHeight="1" spans="1:17">
       <c r="A36" s="50"/>
       <c r="B36" s="33" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C36" s="33" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="32"/>
       <c r="E36" s="34" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="F36" s="51"/>
       <c r="G36" s="51"/>
@@ -11358,14 +11364,14 @@
     <row r="37" ht="13.95" customHeight="1" spans="1:17">
       <c r="A37" s="50"/>
       <c r="B37" s="33" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D37" s="32"/>
       <c r="E37" s="34" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F37" s="51"/>
       <c r="G37" s="51"/>
@@ -11374,22 +11380,22 @@
       <c r="J37" s="42"/>
       <c r="K37" s="5"/>
       <c r="L37" s="33" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M37" s="33" t="s">
         <v>25</v>
       </c>
       <c r="N37" s="33" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="O37" s="33" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="P37" s="54" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="Q37" s="54" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="38" ht="13.95" customHeight="1" spans="1:17">
@@ -11402,7 +11408,7 @@
       </c>
       <c r="D38" s="32"/>
       <c r="E38" s="34" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F38" s="51"/>
       <c r="G38" s="51"/>
@@ -11420,14 +11426,14 @@
     <row r="39" ht="13.95" customHeight="1" spans="1:17">
       <c r="A39" s="50"/>
       <c r="B39" s="33" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C39" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D39" s="32"/>
       <c r="E39" s="34" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F39" s="51"/>
       <c r="G39" s="51"/>
@@ -11800,12 +11806,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -11891,16 +11897,16 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B6" s="32" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D6" s="55">
         <v>7</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
@@ -11916,16 +11922,16 @@
     </row>
     <row r="7" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B7" s="32" t="s">
+        <v>803</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>801</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>799</v>
       </c>
       <c r="D7" s="55">
         <v>7</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
@@ -11941,16 +11947,16 @@
     </row>
     <row r="8" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B8" s="32" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D8" s="55">
         <v>200</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
@@ -11966,16 +11972,16 @@
     </row>
     <row r="9" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B9" s="32" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D9" s="55">
         <v>100</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
@@ -11991,16 +11997,16 @@
     </row>
     <row r="10" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B10" s="32" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D10" s="55">
         <v>100</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
@@ -12017,16 +12023,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="50"/>
       <c r="B11" s="32" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D11" s="55">
         <v>40</v>
       </c>
       <c r="E11" s="56" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
@@ -12043,16 +12049,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="50"/>
       <c r="B12" s="32" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D12" s="55">
         <v>10</v>
       </c>
       <c r="E12" s="56" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F12" s="51"/>
       <c r="G12" s="51"/>
@@ -12069,16 +12075,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="50"/>
       <c r="B13" s="32" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D13" s="55">
         <v>10</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="51"/>
@@ -12095,16 +12101,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="50"/>
       <c r="B14" s="32" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D14" s="55">
         <v>800</v>
       </c>
       <c r="E14" s="56" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="51"/>
@@ -12121,16 +12127,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="50"/>
       <c r="B15" s="32" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D15" s="55">
         <v>1</v>
       </c>
       <c r="E15" s="56" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="51"/>
@@ -12147,14 +12153,14 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="50"/>
       <c r="B16" s="32" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>201</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="56" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F16" s="51"/>
       <c r="G16" s="51"/>
@@ -12171,16 +12177,16 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="50"/>
       <c r="B17" s="32" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D17" s="55">
         <v>64</v>
       </c>
       <c r="E17" s="56" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F17" s="51"/>
       <c r="G17" s="51"/>
@@ -12188,37 +12194,37 @@
       <c r="I17" s="53"/>
       <c r="J17" s="42"/>
       <c r="L17" s="33" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M17" s="33" t="s">
         <v>25</v>
       </c>
       <c r="N17" s="33" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="O17" s="57" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="P17" s="54" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="Q17" s="54" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="50"/>
       <c r="B18" s="32" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D18" s="55">
         <v>20</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F18" s="51"/>
       <c r="G18" s="51"/>
@@ -12235,16 +12241,16 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="50"/>
       <c r="B19" s="32" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D19" s="55">
         <v>7</v>
       </c>
       <c r="E19" s="56" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F19" s="51"/>
       <c r="G19" s="51"/>
@@ -12264,7 +12270,7 @@
         <v>83</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D20" s="55">
         <v>7</v>
@@ -12287,16 +12293,16 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="50"/>
       <c r="B21" s="32" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D21" s="55">
         <v>80</v>
       </c>
       <c r="E21" s="56" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F21" s="51"/>
       <c r="G21" s="51"/>
@@ -12313,16 +12319,16 @@
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="50"/>
       <c r="B22" s="32" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D22" s="55">
         <v>30</v>
       </c>
       <c r="E22" s="56" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F22" s="51"/>
       <c r="G22" s="51"/>
@@ -12339,16 +12345,16 @@
     <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="50"/>
       <c r="B23" s="32" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D23" s="55">
         <v>30</v>
       </c>
       <c r="E23" s="56" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F23" s="51"/>
       <c r="G23" s="51"/>
@@ -12365,16 +12371,16 @@
     <row r="24" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A24" s="50"/>
       <c r="B24" s="32" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D24" s="55">
         <v>40</v>
       </c>
       <c r="E24" s="56" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F24" s="51"/>
       <c r="G24" s="51"/>
@@ -12391,16 +12397,16 @@
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="50"/>
       <c r="B25" s="32" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D25" s="55">
         <v>30</v>
       </c>
       <c r="E25" s="56" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="F25" s="51"/>
       <c r="G25" s="51"/>
@@ -12783,7 +12789,7 @@
         <v>400</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D6" s="26">
         <v>6</v>
@@ -12806,7 +12812,7 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="50"/>
       <c r="B7" s="25" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>201</v>
@@ -12815,7 +12821,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="F7" s="51"/>
       <c r="G7" s="51"/>
@@ -12832,16 +12838,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="50"/>
       <c r="B8" s="25" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D8" s="26">
         <v>8</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="F8" s="51"/>
       <c r="G8" s="51"/>
@@ -12858,7 +12864,7 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="50"/>
       <c r="B9" s="25" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>201</v>
@@ -12867,7 +12873,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -12884,7 +12890,7 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="50"/>
       <c r="B10" s="25" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>201</v>
@@ -12893,7 +12899,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -13452,12 +13458,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -13549,7 +13555,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D6" s="26">
         <v>20</v>
@@ -13573,10 +13579,10 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="25" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D7" s="26">
         <v>100</v>
@@ -13600,7 +13606,7 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="25" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>201</v>
@@ -13609,7 +13615,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="28"/>
@@ -13627,7 +13633,7 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="25" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>201</v>
@@ -13636,7 +13642,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="28"/>
@@ -13654,7 +13660,7 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>201</v>
@@ -13663,7 +13669,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="28"/>
@@ -13681,7 +13687,7 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="25" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>201</v>
@@ -13690,7 +13696,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="28"/>
@@ -13708,7 +13714,7 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>201</v>
@@ -13717,7 +13723,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="28"/>
@@ -13735,16 +13741,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="25" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D13" s="26">
         <v>2</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="28"/>
@@ -13762,16 +13768,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="25" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="28"/>
@@ -13789,16 +13795,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D15" s="26">
         <v>60</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" s="28"/>
@@ -13816,7 +13822,7 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>201</v>
@@ -13825,7 +13831,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="F16" s="28"/>
       <c r="G16" s="28"/>
@@ -13843,16 +13849,16 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="24"/>
       <c r="B17" s="25" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D17" s="26">
         <v>1</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F17" s="28"/>
       <c r="G17" s="28"/>
@@ -13870,16 +13876,16 @@
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="24"/>
       <c r="B18" s="25" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D18" s="26">
         <v>254</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
@@ -13897,16 +13903,16 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="24"/>
       <c r="B19" s="25" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D19" s="26">
         <v>2</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" s="28"/>
@@ -13924,16 +13930,16 @@
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="24"/>
       <c r="B20" s="25" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D20" s="26">
         <v>2</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" s="28"/>
@@ -13951,16 +13957,16 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="24"/>
       <c r="B21" s="25" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D21" s="26">
         <v>10</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" s="28"/>
@@ -13978,16 +13984,16 @@
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="24"/>
       <c r="B22" s="25" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D22" s="26">
         <v>100</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="F22" s="28"/>
       <c r="G22" s="28"/>
@@ -14005,16 +14011,16 @@
     <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="24"/>
       <c r="B23" s="25" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D23" s="26">
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
@@ -14032,16 +14038,16 @@
     <row r="24" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A24" s="24"/>
       <c r="B24" s="25" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D24" s="26">
         <v>2</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
@@ -14059,7 +14065,7 @@
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="24"/>
       <c r="B25" s="25" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>201</v>
@@ -14068,7 +14074,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F25" s="28"/>
       <c r="G25" s="28"/>
@@ -14086,7 +14092,7 @@
     <row r="26" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="24"/>
       <c r="B26" s="25" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>201</v>
@@ -14095,7 +14101,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F26" s="28"/>
       <c r="G26" s="28"/>
@@ -14113,7 +14119,7 @@
     <row r="27" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="24"/>
       <c r="B27" s="25" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>201</v>
@@ -14122,7 +14128,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="F27" s="28"/>
       <c r="G27" s="28"/>
@@ -14140,7 +14146,7 @@
     <row r="28" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A28" s="24"/>
       <c r="B28" s="25" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>201</v>
@@ -14149,7 +14155,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
@@ -14167,7 +14173,7 @@
     <row r="29" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A29" s="24"/>
       <c r="B29" s="25" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C29" s="25" t="s">
         <v>201</v>
@@ -14176,7 +14182,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F29" s="28"/>
       <c r="G29" s="28"/>
@@ -14194,16 +14200,16 @@
     <row r="30" s="5" customFormat="1" ht="13" customHeight="1" spans="1:17">
       <c r="A30" s="24"/>
       <c r="B30" s="25" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D30" s="26">
         <v>20</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F30" s="28"/>
       <c r="G30" s="28"/>
@@ -14221,16 +14227,16 @@
     <row r="31" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A31" s="24"/>
       <c r="B31" s="25" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D31" s="26">
         <v>7</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F31" s="28"/>
       <c r="G31" s="28"/>
@@ -14248,16 +14254,16 @@
     <row r="32" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A32" s="24"/>
       <c r="B32" s="25" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D32" s="26">
         <v>20</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" s="28"/>
@@ -14588,12 +14594,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -14682,16 +14688,16 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="24"/>
       <c r="B6" s="25" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D6" s="26">
         <v>8</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="28"/>
@@ -14712,7 +14718,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D7" s="26">
         <v>20</v>
@@ -14739,7 +14745,7 @@
         <v>83</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D8" s="49">
         <v>7</v>
@@ -15038,12 +15044,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -15135,7 +15141,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D6" s="26">
         <v>20</v>
@@ -15159,16 +15165,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="25" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D7" s="26">
         <v>20</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="28"/>
@@ -15186,16 +15192,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="25" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D8" s="26">
         <v>6</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="28"/>
@@ -15213,16 +15219,16 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="25" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D9" s="26">
         <v>1</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="28"/>
@@ -15240,16 +15246,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D10" s="26">
         <v>20</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="28"/>
@@ -15267,16 +15273,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="25" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D11" s="26">
         <v>10</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="28"/>
@@ -15294,16 +15300,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D12" s="26">
         <v>10</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="28"/>
@@ -15321,16 +15327,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="25" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D13" s="26">
         <v>8</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="28"/>
@@ -15351,7 +15357,7 @@
         <v>83</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D14" s="26">
         <v>4</v>
@@ -15602,39 +15608,39 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -15643,61 +15649,61 @@
         <v>307</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -15705,7 +15711,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -15713,7 +15719,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -23278,10 +23284,16 @@
       <c r="Q24" s="46"/>
     </row>
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B25" s="60"/>
+      <c r="B25" s="60" t="s">
+        <v>585</v>
+      </c>
       <c r="C25" s="61"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
+      <c r="D25" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="E25" s="84" t="s">
+        <v>586</v>
+      </c>
       <c r="F25" s="14"/>
       <c r="G25" s="13"/>
       <c r="H25" s="52"/>
@@ -23359,68 +23371,68 @@
       <c r="I28" s="11"/>
       <c r="J28" s="13"/>
       <c r="L28" s="32" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M28" s="94" t="s">
         <v>519</v>
       </c>
       <c r="N28" s="93" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="P28" s="43"/>
       <c r="Q28" s="18"/>
     </row>
     <row r="29" s="4" customFormat="1" spans="1:17">
       <c r="L29" s="32" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M29" s="95" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N29" s="93" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O29" s="34" t="s">
         <v>155</v>
       </c>
       <c r="P29" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Q29" s="18"/>
     </row>
     <row r="30" s="4" customFormat="1" spans="1:17">
       <c r="L30" s="32" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M30" s="95" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N30" s="93" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O30" s="34" t="s">
         <v>155</v>
       </c>
       <c r="P30" s="43" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="Q30" s="18"/>
     </row>
     <row r="31" ht="13.95" customHeight="1" spans="1:17">
       <c r="L31" s="32" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M31" s="96" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N31" s="93" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O31" s="34" t="s">
         <v>155</v>
       </c>
       <c r="P31" s="44" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Q31" s="18"/>
     </row>
@@ -23429,16 +23441,16 @@
         <v>564</v>
       </c>
       <c r="M32" s="96" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N32" s="46" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="O32" s="46" t="s">
         <v>155</v>
       </c>
       <c r="P32" s="44" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="Q32" s="18"/>
     </row>
@@ -23494,7 +23506,7 @@
     </row>
     <row r="39" ht="56" customHeight="1" spans="2:17">
       <c r="L39" s="48" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
@@ -23535,7 +23547,7 @@
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11"/>
@@ -23769,7 +23781,7 @@
       <c r="J52" s="91"/>
       <c r="K52" s="5"/>
       <c r="L52" s="33" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M52" s="33" t="s">
         <v>551</v>
@@ -23799,7 +23811,7 @@
       <c r="J53" s="90"/>
       <c r="K53" s="86"/>
       <c r="L53" s="33" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M53" s="33" t="s">
         <v>551</v>
@@ -23829,16 +23841,16 @@
       <c r="J54" s="42"/>
       <c r="K54" s="5"/>
       <c r="L54" s="33" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M54" s="33" t="s">
         <v>551</v>
       </c>
       <c r="N54" s="33" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="O54" s="33" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="P54" s="33"/>
       <c r="Q54" s="32"/>
@@ -23861,7 +23873,7 @@
       <c r="J55" s="42"/>
       <c r="K55" s="5"/>
       <c r="L55" s="33" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M55" s="33" t="s">
         <v>551</v>
@@ -23891,13 +23903,13 @@
       <c r="J56" s="42"/>
       <c r="K56" s="5"/>
       <c r="L56" s="33" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M56" s="33" t="s">
         <v>561</v>
       </c>
       <c r="N56" s="33" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O56" s="33"/>
       <c r="P56" s="33"/>
@@ -23905,14 +23917,14 @@
     </row>
     <row r="57" ht="13.95" customHeight="1" spans="2:17">
       <c r="B57" s="32" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C57" s="32"/>
       <c r="D57" s="32" t="s">
         <v>403</v>
       </c>
       <c r="E57" s="84" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F57" s="51"/>
       <c r="G57" s="51"/>
@@ -23929,14 +23941,14 @@
     </row>
     <row r="58" ht="13.95" customHeight="1" spans="2:17">
       <c r="B58" s="32" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C58" s="32"/>
       <c r="D58" s="32" t="s">
         <v>403</v>
       </c>
       <c r="E58" s="84" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F58" s="51"/>
       <c r="G58" s="51"/>
@@ -23953,14 +23965,14 @@
     </row>
     <row r="59" ht="13.95" customHeight="1" spans="2:17">
       <c r="B59" s="32" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C59" s="32"/>
       <c r="D59" s="32" t="s">
         <v>403</v>
       </c>
       <c r="E59" s="84" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F59" s="51"/>
       <c r="G59" s="51"/>
@@ -23993,13 +24005,13 @@
       <c r="J60" s="42"/>
       <c r="K60" s="5"/>
       <c r="L60" s="33" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M60" s="33" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N60" s="33" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="O60" s="33"/>
       <c r="P60" s="33"/>
@@ -24053,7 +24065,7 @@
       <c r="J62" s="42"/>
       <c r="K62" s="5"/>
       <c r="L62" s="33" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M62" s="33" t="s">
         <v>565</v>
@@ -24083,7 +24095,7 @@
       <c r="J63" s="42"/>
       <c r="K63" s="5"/>
       <c r="L63" s="33" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M63" s="33" t="s">
         <v>565</v>
@@ -24117,7 +24129,7 @@
       <c r="N64" s="97"/>
       <c r="O64" s="97"/>
       <c r="P64" s="33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="Q64" s="54"/>
     </row>
@@ -24143,7 +24155,7 @@
       <c r="N65" s="97"/>
       <c r="O65" s="97"/>
       <c r="P65" s="33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="Q65" s="54"/>
     </row>
@@ -24193,7 +24205,7 @@
       <c r="N67" s="97"/>
       <c r="O67" s="97"/>
       <c r="P67" s="33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="Q67" s="54"/>
     </row>
@@ -24238,17 +24250,17 @@
       <c r="E69" s="73" t="s">
         <v>583</v>
       </c>
-      <c r="F69" s="14"/>
-      <c r="G69" s="13"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
       <c r="H69" s="52"/>
       <c r="I69" s="53"/>
       <c r="J69" s="42"/>
       <c r="K69" s="5"/>
       <c r="L69" s="33" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M69" s="33" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N69" s="33" t="s">
         <v>584</v>
@@ -24258,12 +24270,18 @@
       <c r="Q69" s="46"/>
     </row>
     <row r="70" ht="13.95" customHeight="1" spans="2:17">
-      <c r="B70" s="60"/>
+      <c r="B70" s="60" t="s">
+        <v>585</v>
+      </c>
       <c r="C70" s="61"/>
-      <c r="D70" s="62"/>
-      <c r="E70" s="62"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="13"/>
+      <c r="D70" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="E70" s="84" t="s">
+        <v>586</v>
+      </c>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
       <c r="H70" s="52"/>
       <c r="I70" s="53"/>
       <c r="J70" s="42"/>
@@ -24464,7 +24482,7 @@
     <row r="87" ht="13.95" customHeight="1"/>
     <row r="88" ht="13.95" customHeight="1"/>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="52">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:J2"/>
@@ -24498,8 +24516,6 @@
     <mergeCell ref="B46:J46"/>
     <mergeCell ref="L46:Q46"/>
     <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F70:G70"/>
     <mergeCell ref="B71:J71"/>
     <mergeCell ref="L71:Q71"/>
     <mergeCell ref="D72:J72"/>
@@ -24573,12 +24589,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -24682,13 +24698,13 @@
       <c r="I6" s="90"/>
       <c r="J6" s="90"/>
       <c r="L6" s="33" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M6" s="32" t="s">
         <v>547</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O6" s="33" t="s">
         <v>382</v>
@@ -24738,16 +24754,16 @@
       <c r="I8" s="90"/>
       <c r="J8" s="90"/>
       <c r="L8" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M8" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O8" s="33" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="P8" s="93"/>
       <c r="Q8" s="32"/>
@@ -24770,13 +24786,13 @@
       <c r="I9" s="42"/>
       <c r="J9" s="91"/>
       <c r="L9" s="33" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M9" s="32" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O9" s="33" t="s">
         <v>312</v>
@@ -24802,13 +24818,13 @@
       <c r="I10" s="42"/>
       <c r="J10" s="91"/>
       <c r="L10" s="33" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="O10" s="33" t="s">
         <v>385</v>
@@ -24834,16 +24850,16 @@
       <c r="I11" s="90"/>
       <c r="J11" s="90"/>
       <c r="L11" s="33" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M11" s="32" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O11" s="81" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P11" s="93"/>
       <c r="Q11" s="32"/>
@@ -24851,14 +24867,14 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="32" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C12" s="32"/>
       <c r="D12" s="32" t="s">
         <v>272</v>
       </c>
       <c r="E12" s="84" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -24866,16 +24882,16 @@
       <c r="I12" s="53"/>
       <c r="J12" s="42"/>
       <c r="L12" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M12" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="O12" s="33" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="P12" s="93"/>
       <c r="Q12" s="32"/>
@@ -24898,16 +24914,16 @@
       <c r="I13" s="53"/>
       <c r="J13" s="42"/>
       <c r="L13" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M13" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="O13" s="33" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="P13" s="54"/>
       <c r="Q13" s="54"/>
@@ -24930,16 +24946,16 @@
       <c r="I14" s="53"/>
       <c r="J14" s="42"/>
       <c r="L14" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M14" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="O14" s="33" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="P14" s="54"/>
       <c r="Q14" s="54"/>
@@ -24962,16 +24978,16 @@
       <c r="I15" s="53"/>
       <c r="J15" s="42"/>
       <c r="L15" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M15" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="O15" s="81" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="P15" s="54"/>
       <c r="Q15" s="54"/>
@@ -24979,7 +24995,7 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="50"/>
       <c r="B16" s="32" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C16" s="32"/>
       <c r="D16" s="32" t="s">
@@ -24994,16 +25010,16 @@
       <c r="I16" s="53"/>
       <c r="J16" s="42"/>
       <c r="L16" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M16" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="O16" s="33" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="P16" s="54"/>
       <c r="Q16" s="54"/>
@@ -25011,14 +25027,14 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="50"/>
       <c r="B17" s="32" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
         <v>40</v>
       </c>
       <c r="E17" s="84" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="F17" s="51"/>
       <c r="G17" s="51"/>
@@ -25026,16 +25042,16 @@
       <c r="I17" s="53"/>
       <c r="J17" s="42"/>
       <c r="L17" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M17" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N17" s="33" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="O17" s="33" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="P17" s="54"/>
       <c r="Q17" s="54"/>
@@ -25043,14 +25059,14 @@
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="50"/>
       <c r="B18" s="32" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C18" s="32"/>
       <c r="D18" s="32" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="84" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F18" s="51"/>
       <c r="G18" s="51"/>
@@ -25067,14 +25083,14 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="50"/>
       <c r="B19" s="32" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C19" s="32"/>
       <c r="D19" s="32" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E19" s="84" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F19" s="51"/>
       <c r="G19" s="51"/>
@@ -25091,33 +25107,33 @@
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="50"/>
       <c r="B20" s="32" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="84" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F20" s="81" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G20" s="51"/>
       <c r="H20" s="52"/>
       <c r="I20" s="53"/>
       <c r="J20" s="42"/>
       <c r="L20" s="33" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M20" s="32" t="s">
         <v>561</v>
       </c>
       <c r="N20" s="33" t="s">
+        <v>660</v>
+      </c>
+      <c r="O20" s="81" t="s">
         <v>658</v>
-      </c>
-      <c r="O20" s="81" t="s">
-        <v>656</v>
       </c>
       <c r="P20" s="54"/>
       <c r="Q20" s="54"/>
@@ -25125,33 +25141,33 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="50"/>
       <c r="B21" s="32" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C21" s="32"/>
       <c r="D21" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="84" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F21" s="81" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G21" s="51"/>
       <c r="H21" s="52"/>
       <c r="I21" s="53"/>
       <c r="J21" s="42"/>
       <c r="L21" s="33" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M21" s="32" t="s">
         <v>561</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="O21" s="81" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="P21" s="54"/>
       <c r="Q21" s="54"/>
@@ -25159,33 +25175,33 @@
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="50"/>
       <c r="B22" s="32" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C22" s="32"/>
       <c r="D22" s="32" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="84" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F22" s="81" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G22" s="51"/>
       <c r="H22" s="52"/>
       <c r="I22" s="53"/>
       <c r="J22" s="42"/>
       <c r="L22" s="33" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M22" s="32" t="s">
         <v>561</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O22" s="81" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="P22" s="54"/>
       <c r="Q22" s="54"/>
@@ -25193,33 +25209,33 @@
     <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="50"/>
       <c r="B23" s="32" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C23" s="32"/>
       <c r="D23" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="84" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G23" s="51"/>
       <c r="H23" s="52"/>
       <c r="I23" s="53"/>
       <c r="J23" s="42"/>
       <c r="L23" s="33" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M23" s="32" t="s">
         <v>561</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="O23" s="33" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="P23" s="54"/>
       <c r="Q23" s="54"/>
@@ -25227,33 +25243,33 @@
     <row r="24" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A24" s="50"/>
       <c r="B24" s="32" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C24" s="32"/>
       <c r="D24" s="32" t="s">
         <v>50</v>
       </c>
       <c r="E24" s="84" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F24" s="81" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G24" s="51"/>
       <c r="H24" s="52"/>
       <c r="I24" s="53"/>
       <c r="J24" s="42"/>
       <c r="L24" s="33" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M24" s="32" t="s">
         <v>561</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O24" s="81" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P24" s="54"/>
       <c r="Q24" s="54"/>
@@ -25261,14 +25277,14 @@
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="50"/>
       <c r="B25" s="32" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32" t="s">
         <v>403</v>
       </c>
       <c r="E25" s="84" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F25" s="51"/>
       <c r="G25" s="51"/>
@@ -25276,16 +25292,16 @@
       <c r="I25" s="53"/>
       <c r="J25" s="42"/>
       <c r="L25" s="33" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M25" s="32" t="s">
         <v>544</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="O25" s="33" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="P25" s="54"/>
       <c r="Q25" s="54"/>
@@ -25293,14 +25309,14 @@
     <row r="26" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="50"/>
       <c r="B26" s="32" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C26" s="32"/>
       <c r="D26" s="32" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="84" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F26" s="51"/>
       <c r="G26" s="51"/>
@@ -25308,16 +25324,16 @@
       <c r="I26" s="53"/>
       <c r="J26" s="42"/>
       <c r="L26" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M26" s="32" t="s">
         <v>551</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="O26" s="33" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="P26" s="54"/>
       <c r="Q26" s="54"/>
@@ -25325,14 +25341,14 @@
     <row r="27" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="50"/>
       <c r="B27" s="32" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C27" s="32"/>
       <c r="D27" s="32" t="s">
         <v>181</v>
       </c>
       <c r="E27" s="84" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="F27" s="51"/>
       <c r="G27" s="51"/>
@@ -25340,16 +25356,16 @@
       <c r="I27" s="53"/>
       <c r="J27" s="42"/>
       <c r="L27" s="33" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M27" s="32" t="s">
         <v>544</v>
       </c>
       <c r="N27" s="33" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="O27" s="81" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="P27" s="54"/>
       <c r="Q27" s="54"/>
@@ -25558,10 +25574,10 @@
       <c r="I38" s="11"/>
       <c r="J38" s="13"/>
       <c r="L38" s="67" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M38" s="68" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N38" s="66" t="s">
         <v>544</v>
@@ -25572,10 +25588,10 @@
     </row>
     <row r="39" s="4" customFormat="1" ht="10.8" customHeight="1" spans="2:17">
       <c r="L39" s="67" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M39" s="68" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N39" s="66" t="s">
         <v>547</v>
@@ -25588,10 +25604,10 @@
     </row>
     <row r="40" s="4" customFormat="1" ht="10.8" customHeight="1" spans="2:17">
       <c r="L40" s="67" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M40" s="68" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N40" s="66" t="s">
         <v>551</v>
@@ -25604,10 +25620,10 @@
     </row>
     <row r="41" ht="13.95" customHeight="1" spans="2:17">
       <c r="L41" s="67" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M41" s="68" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N41" s="66" t="s">
         <v>561</v>
@@ -25620,13 +25636,13 @@
     </row>
     <row r="42" ht="13.95" customHeight="1" spans="2:17">
       <c r="L42" s="67" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M42" s="68" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N42" s="66" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O42" s="66" t="s">
         <v>155</v>
@@ -25686,7 +25702,7 @@
     </row>
     <row r="49" ht="56" customHeight="1" spans="12:17">
       <c r="L49" s="48" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M49" s="17"/>
       <c r="N49" s="17"/>
@@ -25775,7 +25791,7 @@
     <mergeCell ref="A9:A12"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19 C27 C28 C9:C18 C20:C26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C28">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/data_assets/mapping/ods_to_dwd/DWD明细层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/ods_to_dwd/DWD明细层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" firstSheet="3" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="客户基本信息" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3440" uniqueCount="1111">
   <si>
     <t>返回目录</t>
   </si>
@@ -2559,10 +2559,13 @@
     <t>t1.SIGN_ACC_NO</t>
   </si>
   <si>
+    <t>SIGN_TYPE</t>
+  </si>
+  <si>
+    <t>签约类型</t>
+  </si>
+  <si>
     <t>CTRAKT_TYP</t>
-  </si>
-  <si>
-    <t>签约类型</t>
   </si>
   <si>
     <t>t1.SIGN_TYPE</t>
@@ -8627,7 +8630,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr defaultColWidth="8.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="6" customWidth="1"/>
@@ -8835,60 +8838,54 @@
       <c r="H8" s="94"/>
       <c r="I8" s="95"/>
       <c r="J8" s="95"/>
-      <c r="L8" s="30" t="s">
-        <v>724</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>725</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>729</v>
-      </c>
+      <c r="L8" s="30"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="30"/>
       <c r="O8" s="32"/>
       <c r="P8" s="30"/>
       <c r="Q8" s="30"/>
     </row>
-    <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="92"/>
+    <row r="9" s="91" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A9" s="24"/>
       <c r="B9" s="30" t="s">
-        <v>730</v>
-      </c>
-      <c r="C9" s="87"/>
+        <v>729</v>
+      </c>
+      <c r="C9" s="93"/>
       <c r="D9" s="30" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" s="89" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="96"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
       <c r="L9" s="30" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="O9" s="32"/>
       <c r="P9" s="30"/>
       <c r="Q9" s="30"/>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="24"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="30" t="s">
-        <v>96</v>
+        <v>731</v>
       </c>
       <c r="C10" s="87"/>
       <c r="D10" s="30" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E10" s="89" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F10" s="30"/>
       <c r="G10" s="30"/>
@@ -8896,89 +8893,89 @@
       <c r="I10" s="44"/>
       <c r="J10" s="96"/>
       <c r="L10" s="30" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N10" s="30" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="O10" s="32"/>
       <c r="P10" s="30"/>
       <c r="Q10" s="30"/>
     </row>
-    <row r="11" s="91" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+    <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="30" t="s">
-        <v>737</v>
-      </c>
-      <c r="C11" s="93"/>
+        <v>96</v>
+      </c>
+      <c r="C11" s="87"/>
       <c r="D11" s="30" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E11" s="89" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="95"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="96"/>
       <c r="L11" s="30" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N11" s="30" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O11" s="32"/>
       <c r="P11" s="30"/>
       <c r="Q11" s="30"/>
     </row>
-    <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+    <row r="12" s="91" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="30" t="s">
-        <v>740</v>
-      </c>
-      <c r="C12" s="87"/>
+        <v>738</v>
+      </c>
+      <c r="C12" s="93"/>
       <c r="D12" s="30" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E12" s="89" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="44"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="95"/>
       <c r="L12" s="30" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M12" s="31" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N12" s="30" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="O12" s="32"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="30"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="92"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="30" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C13" s="87"/>
       <c r="D13" s="30" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="E13" s="89" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="30"/>
@@ -8986,48 +8983,60 @@
       <c r="I13" s="58"/>
       <c r="J13" s="44"/>
       <c r="L13" s="30" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="M13" s="31" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="N13" s="30" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O13" s="32"/>
       <c r="P13" s="30"/>
       <c r="Q13" s="30"/>
     </row>
-    <row r="14" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
+    <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="92"/>
       <c r="B14" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="88"/>
-      <c r="D14" s="97" t="s">
-        <v>86</v>
+        <v>744</v>
+      </c>
+      <c r="C14" s="87"/>
+      <c r="D14" s="30" t="s">
+        <v>52</v>
       </c>
       <c r="E14" s="89" t="s">
-        <v>87</v>
+        <v>745</v>
       </c>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
       <c r="H14" s="25"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="96"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="31"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="44"/>
+      <c r="L14" s="30" t="s">
+        <v>724</v>
+      </c>
+      <c r="M14" s="31" t="s">
+        <v>725</v>
+      </c>
+      <c r="N14" s="30" t="s">
+        <v>746</v>
+      </c>
       <c r="O14" s="32"/>
       <c r="P14" s="30"/>
       <c r="Q14" s="30"/>
     </row>
     <row r="15" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="24"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="88"/>
+      <c r="D15" s="97" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="89" t="s">
+        <v>87</v>
+      </c>
       <c r="F15" s="30"/>
       <c r="G15" s="30"/>
       <c r="H15" s="25"/>
@@ -9040,145 +9049,155 @@
       <c r="P15" s="30"/>
       <c r="Q15" s="30"/>
     </row>
-    <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B16" s="65"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="13"/>
+    <row r="16" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
+      <c r="A16" s="24"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="25"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="44"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="48"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="17.4" customHeight="1" spans="2:17">
-      <c r="B17" s="9" t="s">
+      <c r="I16" s="44"/>
+      <c r="J16" s="96"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+    </row>
+    <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="2:17">
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="44"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="48"/>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="17.4" customHeight="1" spans="2:17">
+      <c r="B18" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="13"/>
-      <c r="L17" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="18"/>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="17.4" customHeight="1" spans="2:17">
-      <c r="B18" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>20</v>
-      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="13"/>
-      <c r="L18" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="M18" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="N18" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="O18" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="P18" s="41" t="s">
-        <v>156</v>
-      </c>
+      <c r="L18" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
       <c r="Q18" s="18"/>
     </row>
-    <row r="19" s="4" customFormat="1" ht="11.4" customHeight="1" spans="2:17">
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="44"/>
+    <row r="19" s="3" customFormat="1" ht="17.4" customHeight="1" spans="2:17">
+      <c r="B19" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>20</v>
+      </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="13"/>
-      <c r="L19" s="30" t="s">
+      <c r="L19" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="M19" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="N19" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="O19" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="P19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q19" s="18"/>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="11.4" customHeight="1" spans="2:17">
+      <c r="B20" s="42"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="13"/>
+      <c r="L20" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="M19" s="30" t="s">
+      <c r="M20" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="N19" s="31" t="s">
+      <c r="N20" s="31" t="s">
         <v>720</v>
       </c>
-      <c r="O19" s="32"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="18"/>
-    </row>
-    <row r="20" s="4" customFormat="1" spans="2:17">
-      <c r="L20" s="30" t="s">
-        <v>732</v>
-      </c>
-      <c r="M20" s="30" t="s">
-        <v>746</v>
-      </c>
-      <c r="N20" s="31" t="s">
-        <v>725</v>
-      </c>
-      <c r="O20" s="32" t="s">
-        <v>747</v>
-      </c>
-      <c r="P20" s="45" t="s">
-        <v>748</v>
-      </c>
+      <c r="O20" s="32"/>
+      <c r="P20" s="45"/>
       <c r="Q20" s="18"/>
     </row>
     <row r="21" s="4" customFormat="1" spans="2:17">
       <c r="L21" s="30" t="s">
+        <v>733</v>
+      </c>
+      <c r="M21" s="30" t="s">
+        <v>747</v>
+      </c>
+      <c r="N21" s="31" t="s">
+        <v>725</v>
+      </c>
+      <c r="O21" s="32" t="s">
+        <v>748</v>
+      </c>
+      <c r="P21" s="45" t="s">
+        <v>749</v>
+      </c>
+      <c r="Q21" s="18"/>
+    </row>
+    <row r="22" s="4" customFormat="1" spans="2:17">
+      <c r="L22" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="M21" s="30" t="s">
-        <v>749</v>
-      </c>
-      <c r="N21" s="31" t="s">
-        <v>733</v>
-      </c>
-      <c r="O21" s="32" t="s">
+      <c r="M22" s="30" t="s">
         <v>750</v>
       </c>
-      <c r="P21" s="45" t="s">
+      <c r="N22" s="31" t="s">
+        <v>734</v>
+      </c>
+      <c r="O22" s="32" t="s">
         <v>751</v>
       </c>
-      <c r="Q21" s="18"/>
-    </row>
-    <row r="22" ht="13.95" customHeight="1" spans="2:17">
-      <c r="P22" s="46"/>
+      <c r="P22" s="45" t="s">
+        <v>752</v>
+      </c>
       <c r="Q22" s="18"/>
     </row>
     <row r="23" ht="13.95" customHeight="1" spans="2:17">
-      <c r="L23" s="47"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
       <c r="P23" s="46"/>
       <c r="Q23" s="18"/>
     </row>
@@ -9215,32 +9234,39 @@
       <c r="Q27" s="18"/>
     </row>
     <row r="28" ht="13.95" customHeight="1" spans="2:17">
-      <c r="L28" s="82"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="84"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
       <c r="O28" s="48"/>
-      <c r="P28" s="85"/>
+      <c r="P28" s="46"/>
       <c r="Q28" s="18"/>
     </row>
     <row r="29" ht="13.95" customHeight="1" spans="2:17">
-      <c r="L29" s="49" t="s">
+      <c r="L29" s="82"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="18"/>
+    </row>
+    <row r="30" ht="13.95" customHeight="1" spans="2:17">
+      <c r="L30" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="18"/>
-    </row>
-    <row r="30" ht="56" customHeight="1" spans="2:17">
-      <c r="L30" s="50"/>
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
       <c r="O30" s="17"/>
       <c r="P30" s="17"/>
       <c r="Q30" s="18"/>
     </row>
-    <row r="31" ht="13.95" customHeight="1"/>
+    <row r="31" ht="56" customHeight="1" spans="2:17">
+      <c r="L31" s="50"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="18"/>
+    </row>
     <row r="32" ht="13.95" customHeight="1"/>
     <row r="33" ht="13.95" customHeight="1"/>
     <row r="34" ht="13.95" customHeight="1"/>
@@ -9289,6 +9315,7 @@
     <row r="77" ht="13.95" customHeight="1"/>
     <row r="78" ht="13.95" customHeight="1"/>
     <row r="79" ht="13.95" customHeight="1"/>
+    <row r="80" ht="13.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="B1:J1"/>
@@ -9298,13 +9325,12 @@
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="L17:Q17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="L18:Q18"/>
     <mergeCell ref="D19:J19"/>
     <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="D20:J20"/>
     <mergeCell ref="P20:Q20"/>
     <mergeCell ref="P21:Q21"/>
     <mergeCell ref="P22:Q22"/>
@@ -9314,14 +9340,15 @@
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="L29:Q29"/>
+    <mergeCell ref="P29:Q29"/>
     <mergeCell ref="L30:Q30"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="L31:Q31"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A15:A16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -9372,12 +9399,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -9517,7 +9544,7 @@
         <v>534</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O7" s="31" t="s">
         <v>29</v>
@@ -9528,14 +9555,14 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="57"/>
       <c r="B8" s="31" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>253</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="32" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F8" s="51"/>
       <c r="G8" s="51"/>
@@ -9543,16 +9570,16 @@
       <c r="I8" s="58"/>
       <c r="J8" s="44"/>
       <c r="L8" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M8" s="31" t="s">
         <v>537</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O8" s="31" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P8" s="59"/>
       <c r="Q8" s="59"/>
@@ -9560,14 +9587,14 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="57"/>
       <c r="B9" s="31" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="32" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -9584,14 +9611,14 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="57"/>
       <c r="B10" s="31" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>338</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="32" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -9599,16 +9626,16 @@
       <c r="I10" s="58"/>
       <c r="J10" s="44"/>
       <c r="L10" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M10" s="31" t="s">
         <v>537</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O10" s="31" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
@@ -9631,7 +9658,7 @@
       <c r="I11" s="58"/>
       <c r="J11" s="44"/>
       <c r="L11" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M11" s="31" t="s">
         <v>537</v>
@@ -9663,7 +9690,7 @@
       <c r="I12" s="58"/>
       <c r="J12" s="44"/>
       <c r="L12" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M12" s="31" t="s">
         <v>537</v>
@@ -9680,14 +9707,14 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="57"/>
       <c r="B13" s="31" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="32" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="51"/>
@@ -9695,16 +9722,16 @@
       <c r="I13" s="58"/>
       <c r="J13" s="44"/>
       <c r="L13" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M13" s="31" t="s">
         <v>537</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O13" s="86" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="P13" s="59"/>
       <c r="Q13" s="59"/>
@@ -10021,19 +10048,19 @@
     </row>
     <row r="30" s="4" customFormat="1" spans="1:17">
       <c r="L30" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M30" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N30" s="71" t="s">
         <v>537</v>
       </c>
       <c r="O30" s="71" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P30" s="45" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Q30" s="18"/>
     </row>
@@ -10249,12 +10276,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -10388,16 +10415,16 @@
       <c r="I7" s="58"/>
       <c r="J7" s="44"/>
       <c r="L7" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M7" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O7" s="31" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P7" s="59"/>
       <c r="Q7" s="59"/>
@@ -10405,10 +10432,10 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="57"/>
       <c r="B8" s="31" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="64" t="s">
@@ -10429,14 +10456,14 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="57"/>
       <c r="B9" s="31" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="64" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -10444,16 +10471,16 @@
       <c r="I9" s="58"/>
       <c r="J9" s="44"/>
       <c r="L9" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O9" s="31" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P9" s="59"/>
       <c r="Q9" s="59"/>
@@ -10461,14 +10488,14 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="57"/>
       <c r="B10" s="63" t="s">
+        <v>780</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>779</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>778</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="64" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -10476,13 +10503,13 @@
       <c r="I10" s="58"/>
       <c r="J10" s="44"/>
       <c r="L10" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="O10" s="31" t="s">
         <v>410</v>
@@ -10496,7 +10523,7 @@
         <v>507</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="64" t="s">
@@ -10508,13 +10535,13 @@
       <c r="I11" s="58"/>
       <c r="J11" s="44"/>
       <c r="L11" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="O11" s="31" t="s">
         <v>508</v>
@@ -10540,10 +10567,10 @@
       <c r="I12" s="58"/>
       <c r="J12" s="44"/>
       <c r="L12" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M12" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N12" s="31" t="s">
         <v>499</v>
@@ -10572,13 +10599,13 @@
       <c r="I13" s="58"/>
       <c r="J13" s="44"/>
       <c r="L13" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M13" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="O13" s="31" t="s">
         <v>334</v>
@@ -10621,14 +10648,14 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="57"/>
       <c r="B15" s="31" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>338</v>
       </c>
       <c r="D15" s="30"/>
       <c r="E15" s="64" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="51"/>
@@ -10636,16 +10663,16 @@
       <c r="I15" s="58"/>
       <c r="J15" s="44"/>
       <c r="L15" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M15" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O15" s="31" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P15" s="59"/>
       <c r="Q15" s="59"/>
@@ -10668,10 +10695,10 @@
       <c r="I16" s="58"/>
       <c r="J16" s="44"/>
       <c r="L16" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M16" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N16" s="31" t="s">
         <v>468</v>
@@ -10700,10 +10727,10 @@
       <c r="I17" s="58"/>
       <c r="J17" s="44"/>
       <c r="L17" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M17" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N17" s="31" t="s">
         <v>476</v>
@@ -10732,16 +10759,16 @@
       <c r="I18" s="58"/>
       <c r="J18" s="44"/>
       <c r="L18" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M18" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="O18" s="31" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P18" s="59"/>
       <c r="Q18" s="59"/>
@@ -10764,16 +10791,16 @@
       <c r="I19" s="58"/>
       <c r="J19" s="44"/>
       <c r="L19" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M19" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="O19" s="31" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P19" s="59"/>
       <c r="Q19" s="59"/>
@@ -10795,10 +10822,10 @@
       <c r="I20" s="58"/>
       <c r="J20" s="44"/>
       <c r="L20" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M20" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N20" s="31"/>
       <c r="O20" s="31"/>
@@ -10807,30 +10834,30 @@
     </row>
     <row r="21" s="5" customFormat="1" ht="32.4" customHeight="1" spans="1:17">
       <c r="B21" s="34" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C21" s="34" t="s">
         <v>185</v>
       </c>
       <c r="D21" s="35"/>
       <c r="E21" s="36" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="I21" s="58"/>
       <c r="J21" s="44"/>
       <c r="L21" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M21" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N21" s="69" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O21" s="69" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P21" s="70"/>
       <c r="Q21" s="48"/>
@@ -10851,13 +10878,13 @@
       <c r="I22" s="58"/>
       <c r="J22" s="44"/>
       <c r="L22" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M22" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N22" s="69" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O22" s="36" t="s">
         <v>23</v>
@@ -10881,13 +10908,13 @@
       <c r="I23" s="58"/>
       <c r="J23" s="44"/>
       <c r="L23" s="31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M23" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N23" s="69" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O23" s="69" t="s">
         <v>323</v>
@@ -10917,7 +10944,7 @@
         <v>512</v>
       </c>
       <c r="N24" s="69" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O24" s="69" t="s">
         <v>402</v>
@@ -11041,16 +11068,16 @@
         <v>448</v>
       </c>
       <c r="M30" s="31" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N30" s="71" t="s">
         <v>537</v>
       </c>
       <c r="O30" s="71" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P30" s="45" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Q30" s="18"/>
     </row>
@@ -11266,12 +11293,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -11373,16 +11400,16 @@
       <c r="I6" s="58"/>
       <c r="J6" s="44"/>
       <c r="L6" s="31" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N6" s="31" t="s">
         <v>535</v>
       </c>
       <c r="O6" s="62" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="P6" s="59"/>
       <c r="Q6" s="59"/>
@@ -11390,14 +11417,14 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="57"/>
       <c r="B7" s="31" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="30"/>
       <c r="E7" s="32" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F7" s="51"/>
       <c r="G7" s="51"/>
@@ -11414,14 +11441,14 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="57"/>
       <c r="B8" s="31" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="32" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F8" s="51"/>
       <c r="G8" s="51"/>
@@ -11429,13 +11456,13 @@
       <c r="I8" s="58"/>
       <c r="J8" s="44"/>
       <c r="L8" s="31" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M8" s="31" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="O8" s="31"/>
       <c r="P8" s="59"/>
@@ -11444,14 +11471,14 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="57"/>
       <c r="B9" s="31" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="32" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -11465,16 +11492,16 @@
         <v>25</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O9" s="31" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P9" s="59" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Q9" s="59" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
@@ -11487,7 +11514,7 @@
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="32" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -11495,16 +11522,16 @@
       <c r="I10" s="58"/>
       <c r="J10" s="44"/>
       <c r="L10" s="31" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="O10" s="31" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
@@ -11512,14 +11539,14 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="57"/>
       <c r="B11" s="31" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="32" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
@@ -11527,16 +11554,16 @@
       <c r="I11" s="58"/>
       <c r="J11" s="44"/>
       <c r="L11" s="31" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N11" s="31" t="s">
+        <v>817</v>
+      </c>
+      <c r="O11" s="62" t="s">
         <v>816</v>
-      </c>
-      <c r="O11" s="62" t="s">
-        <v>815</v>
       </c>
       <c r="P11" s="59"/>
       <c r="Q11" s="59"/>
@@ -11559,16 +11586,16 @@
       <c r="I12" s="58"/>
       <c r="J12" s="44"/>
       <c r="L12" s="31" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M12" s="31" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O12" s="62" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="P12" s="59"/>
       <c r="Q12" s="59"/>
@@ -11791,12 +11818,12 @@
         <v>1</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
@@ -11927,14 +11954,14 @@
     <row r="35" ht="13.95" customHeight="1" spans="1:17">
       <c r="A35" s="57"/>
       <c r="B35" s="31" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>32</v>
       </c>
       <c r="D35" s="30"/>
       <c r="E35" s="32" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F35" s="51"/>
       <c r="G35" s="51"/>
@@ -11952,14 +11979,14 @@
     <row r="36" ht="13.95" customHeight="1" spans="1:17">
       <c r="A36" s="57"/>
       <c r="B36" s="31" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="30"/>
       <c r="E36" s="32" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F36" s="51"/>
       <c r="G36" s="51"/>
@@ -11977,14 +12004,14 @@
     <row r="37" ht="13.95" customHeight="1" spans="1:17">
       <c r="A37" s="57"/>
       <c r="B37" s="31" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D37" s="30"/>
       <c r="E37" s="32" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F37" s="51"/>
       <c r="G37" s="51"/>
@@ -11999,16 +12026,16 @@
         <v>25</v>
       </c>
       <c r="N37" s="31" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O37" s="31" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P37" s="59" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Q37" s="59" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="38" ht="13.95" customHeight="1" spans="1:17">
@@ -12021,7 +12048,7 @@
       </c>
       <c r="D38" s="30"/>
       <c r="E38" s="32" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F38" s="51"/>
       <c r="G38" s="51"/>
@@ -12039,14 +12066,14 @@
     <row r="39" ht="13.95" customHeight="1" spans="1:17">
       <c r="A39" s="57"/>
       <c r="B39" s="31" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>40</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="32" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F39" s="51"/>
       <c r="G39" s="51"/>
@@ -12419,12 +12446,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -12510,16 +12537,16 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B6" s="30" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="60">
         <v>7</v>
       </c>
       <c r="E6" s="61" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
@@ -12535,16 +12562,16 @@
     </row>
     <row r="7" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B7" s="30" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="60">
         <v>7</v>
       </c>
       <c r="E7" s="61" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
@@ -12560,16 +12587,16 @@
     </row>
     <row r="8" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B8" s="30" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="60">
         <v>200</v>
       </c>
       <c r="E8" s="61" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
@@ -12585,16 +12612,16 @@
     </row>
     <row r="9" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B9" s="30" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="60">
         <v>100</v>
       </c>
       <c r="E9" s="61" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
@@ -12610,16 +12637,16 @@
     </row>
     <row r="10" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
       <c r="B10" s="30" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="60">
         <v>100</v>
       </c>
       <c r="E10" s="61" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
@@ -12636,16 +12663,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="57"/>
       <c r="B11" s="30" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="60">
         <v>40</v>
       </c>
       <c r="E11" s="61" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
@@ -12662,16 +12689,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="57"/>
       <c r="B12" s="30" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="60">
         <v>10</v>
       </c>
       <c r="E12" s="61" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F12" s="51"/>
       <c r="G12" s="51"/>
@@ -12688,16 +12715,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="57"/>
       <c r="B13" s="30" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="60">
         <v>10</v>
       </c>
       <c r="E13" s="61" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="51"/>
@@ -12714,16 +12741,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="57"/>
       <c r="B14" s="30" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="60">
         <v>800</v>
       </c>
       <c r="E14" s="61" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="51"/>
@@ -12740,16 +12767,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="57"/>
       <c r="B15" s="30" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="60">
         <v>1</v>
       </c>
       <c r="E15" s="61" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="51"/>
@@ -12766,14 +12793,14 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="57"/>
       <c r="B16" s="30" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C16" s="30" t="s">
         <v>205</v>
       </c>
       <c r="D16" s="60"/>
       <c r="E16" s="61" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F16" s="51"/>
       <c r="G16" s="51"/>
@@ -12790,16 +12817,16 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="57"/>
       <c r="B17" s="30" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D17" s="60">
         <v>64</v>
       </c>
       <c r="E17" s="61" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F17" s="51"/>
       <c r="G17" s="51"/>
@@ -12807,37 +12834,37 @@
       <c r="I17" s="58"/>
       <c r="J17" s="44"/>
       <c r="L17" s="31" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M17" s="31" t="s">
         <v>25</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="O17" s="62" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="P17" s="59" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Q17" s="59" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="57"/>
       <c r="B18" s="30" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D18" s="60">
         <v>20</v>
       </c>
       <c r="E18" s="61" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F18" s="51"/>
       <c r="G18" s="51"/>
@@ -12854,16 +12881,16 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="57"/>
       <c r="B19" s="30" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D19" s="60">
         <v>7</v>
       </c>
       <c r="E19" s="61" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F19" s="51"/>
       <c r="G19" s="51"/>
@@ -12883,7 +12910,7 @@
         <v>85</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D20" s="60">
         <v>7</v>
@@ -12906,16 +12933,16 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="57"/>
       <c r="B21" s="30" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D21" s="60">
         <v>80</v>
       </c>
       <c r="E21" s="61" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F21" s="51"/>
       <c r="G21" s="51"/>
@@ -12932,16 +12959,16 @@
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="57"/>
       <c r="B22" s="30" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D22" s="60">
         <v>30</v>
       </c>
       <c r="E22" s="61" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F22" s="51"/>
       <c r="G22" s="51"/>
@@ -12958,16 +12985,16 @@
     <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="57"/>
       <c r="B23" s="30" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D23" s="60">
         <v>30</v>
       </c>
       <c r="E23" s="61" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F23" s="51"/>
       <c r="G23" s="51"/>
@@ -12984,16 +13011,16 @@
     <row r="24" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A24" s="57"/>
       <c r="B24" s="30" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D24" s="60">
         <v>40</v>
       </c>
       <c r="E24" s="61" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F24" s="51"/>
       <c r="G24" s="51"/>
@@ -13010,16 +13037,16 @@
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="57"/>
       <c r="B25" s="30" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D25" s="60">
         <v>30</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="F25" s="51"/>
       <c r="G25" s="51"/>
@@ -13399,16 +13426,16 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="57"/>
       <c r="B6" s="34" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>6</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
@@ -13425,7 +13452,7 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="57"/>
       <c r="B7" s="34" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>205</v>
@@ -13434,7 +13461,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F7" s="51"/>
       <c r="G7" s="51"/>
@@ -13451,16 +13478,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="57"/>
       <c r="B8" s="34" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="35">
         <v>8</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F8" s="51"/>
       <c r="G8" s="51"/>
@@ -13477,7 +13504,7 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="57"/>
       <c r="B9" s="34" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C9" s="34" t="s">
         <v>205</v>
@@ -13486,7 +13513,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
@@ -13503,7 +13530,7 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="57"/>
       <c r="B10" s="34" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>205</v>
@@ -13512,7 +13539,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F10" s="51"/>
       <c r="G10" s="51"/>
@@ -14071,12 +14098,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -14168,7 +14195,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>20</v>
@@ -14192,10 +14219,10 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="34" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="35">
         <v>100</v>
@@ -14219,7 +14246,7 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="34" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>205</v>
@@ -14228,7 +14255,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F8" s="35"/>
       <c r="G8" s="27"/>
@@ -14246,7 +14273,7 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="34" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C9" s="34" t="s">
         <v>205</v>
@@ -14255,7 +14282,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F9" s="35"/>
       <c r="G9" s="27"/>
@@ -14273,7 +14300,7 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="34" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>205</v>
@@ -14282,7 +14309,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F10" s="35"/>
       <c r="G10" s="27"/>
@@ -14300,7 +14327,7 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="34" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>205</v>
@@ -14309,7 +14336,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F11" s="35"/>
       <c r="G11" s="27"/>
@@ -14327,7 +14354,7 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="34" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>205</v>
@@ -14336,7 +14363,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="27"/>
@@ -14354,16 +14381,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="34" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="35">
         <v>2</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F13" s="35"/>
       <c r="G13" s="27"/>
@@ -14381,16 +14408,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="34" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="35">
         <v>2</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F14" s="35"/>
       <c r="G14" s="27"/>
@@ -14408,16 +14435,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="34" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="35">
         <v>60</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F15" s="27"/>
       <c r="G15" s="27"/>
@@ -14435,7 +14462,7 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="24"/>
       <c r="B16" s="34" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C16" s="34" t="s">
         <v>205</v>
@@ -14444,7 +14471,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
@@ -14462,16 +14489,16 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="24"/>
       <c r="B17" s="34" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D17" s="35">
         <v>1</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
@@ -14489,16 +14516,16 @@
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="24"/>
       <c r="B18" s="34" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D18" s="35">
         <v>254</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F18" s="27"/>
       <c r="G18" s="27"/>
@@ -14516,16 +14543,16 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="24"/>
       <c r="B19" s="34" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D19" s="35">
         <v>2</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
@@ -14543,16 +14570,16 @@
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="24"/>
       <c r="B20" s="34" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D20" s="35">
         <v>2</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
@@ -14570,16 +14597,16 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="24"/>
       <c r="B21" s="34" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D21" s="35">
         <v>10</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F21" s="27"/>
       <c r="G21" s="27"/>
@@ -14597,16 +14624,16 @@
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="24"/>
       <c r="B22" s="34" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D22" s="35">
         <v>100</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="27"/>
@@ -14624,16 +14651,16 @@
     <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="24"/>
       <c r="B23" s="34" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D23" s="35">
         <v>2</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F23" s="27"/>
       <c r="G23" s="27"/>
@@ -14651,16 +14678,16 @@
     <row r="24" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A24" s="24"/>
       <c r="B24" s="34" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D24" s="35">
         <v>2</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F24" s="27"/>
       <c r="G24" s="27"/>
@@ -14678,7 +14705,7 @@
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="24"/>
       <c r="B25" s="34" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>205</v>
@@ -14687,7 +14714,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F25" s="27"/>
       <c r="G25" s="27"/>
@@ -14705,7 +14732,7 @@
     <row r="26" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="24"/>
       <c r="B26" s="34" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>205</v>
@@ -14714,7 +14741,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
@@ -14732,7 +14759,7 @@
     <row r="27" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="24"/>
       <c r="B27" s="34" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>205</v>
@@ -14741,7 +14768,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
@@ -14759,7 +14786,7 @@
     <row r="28" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A28" s="24"/>
       <c r="B28" s="34" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>205</v>
@@ -14768,7 +14795,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
@@ -14786,7 +14813,7 @@
     <row r="29" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A29" s="24"/>
       <c r="B29" s="34" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C29" s="34" t="s">
         <v>205</v>
@@ -14795,7 +14822,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
@@ -14813,16 +14840,16 @@
     <row r="30" s="5" customFormat="1" ht="13" customHeight="1" spans="1:17">
       <c r="A30" s="24"/>
       <c r="B30" s="34" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D30" s="35">
         <v>20</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
@@ -14840,16 +14867,16 @@
     <row r="31" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A31" s="24"/>
       <c r="B31" s="34" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D31" s="35">
         <v>7</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
@@ -14867,16 +14894,16 @@
     <row r="32" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A32" s="24"/>
       <c r="B32" s="34" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D32" s="35">
         <v>20</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
@@ -15207,12 +15234,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -15304,7 +15331,7 @@
         <v>305</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>8</v>
@@ -15331,7 +15358,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="35">
         <v>20</v>
@@ -15358,7 +15385,7 @@
         <v>85</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="56">
         <v>7</v>
@@ -15657,12 +15684,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -15754,7 +15781,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>20</v>
@@ -15778,16 +15805,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="34" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="35">
         <v>20</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="27"/>
@@ -15805,16 +15832,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="34" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="35">
         <v>6</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F8" s="35"/>
       <c r="G8" s="27"/>
@@ -15832,16 +15859,16 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="34" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="35">
         <v>1</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F9" s="35"/>
       <c r="G9" s="27"/>
@@ -15859,16 +15886,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="34" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="35">
         <v>20</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F10" s="35"/>
       <c r="G10" s="27"/>
@@ -15886,16 +15913,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="34" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="35">
         <v>10</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F11" s="35"/>
       <c r="G11" s="27"/>
@@ -15913,16 +15940,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="34" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="35">
         <v>10</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="27"/>
@@ -15940,16 +15967,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="34" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="35">
         <v>8</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F13" s="35"/>
       <c r="G13" s="27"/>
@@ -15970,7 +15997,7 @@
         <v>85</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="35">
         <v>4</v>
@@ -16250,12 +16277,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -16344,16 +16371,16 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="24"/>
       <c r="B6" s="55" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>40</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F6" s="35"/>
       <c r="G6" s="27"/>
@@ -16371,16 +16398,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="55" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="35">
         <v>40</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="27"/>
@@ -16401,7 +16428,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="35">
         <v>21</v>
@@ -16428,7 +16455,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="35">
         <v>200</v>
@@ -16452,16 +16479,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="34" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="35">
         <v>1</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F10" s="35"/>
       <c r="G10" s="27"/>
@@ -16479,16 +16506,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="55" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F11" s="35"/>
       <c r="G11" s="27"/>
@@ -16506,16 +16533,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="55" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="35">
         <v>30</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="27"/>
@@ -16533,16 +16560,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="55" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="35">
         <v>30</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F13" s="35"/>
       <c r="G13" s="27"/>
@@ -16560,16 +16587,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="55" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="35">
         <v>64</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F14" s="35"/>
       <c r="G14" s="27"/>
@@ -16587,16 +16614,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="55" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="35">
         <v>20</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F15" s="35"/>
       <c r="G15" s="27"/>
@@ -16614,16 +16641,16 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="24"/>
       <c r="B16" s="55" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D16" s="35">
         <v>30</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F16" s="35"/>
       <c r="G16" s="27"/>
@@ -16641,7 +16668,7 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="24"/>
       <c r="B17" s="55" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C17" s="34" t="s">
         <v>205</v>
@@ -16650,7 +16677,7 @@
         <v>18</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F17" s="35"/>
       <c r="G17" s="27"/>
@@ -16668,7 +16695,7 @@
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="24"/>
       <c r="B18" s="55" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C18" s="34" t="s">
         <v>205</v>
@@ -16677,7 +16704,7 @@
         <v>18</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F18" s="35"/>
       <c r="G18" s="27"/>
@@ -16698,7 +16725,7 @@
         <v>305</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D19" s="35">
         <v>30</v>
@@ -16725,7 +16752,7 @@
         <v>85</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D20" s="35">
         <v>30</v>
@@ -16749,10 +16776,10 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="24"/>
       <c r="B21" s="54" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D21" s="35">
         <v>2000</v>
@@ -18627,12 +18654,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -18721,16 +18748,16 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="24"/>
       <c r="B6" s="34" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>40</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F6" s="35"/>
       <c r="G6" s="27"/>
@@ -18748,16 +18775,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="34" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="35">
         <v>200</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="27"/>
@@ -18775,16 +18802,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="34" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="35">
         <v>50</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F8" s="35"/>
       <c r="G8" s="27"/>
@@ -18802,16 +18829,16 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="34" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="35">
         <v>10</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F9" s="35"/>
       <c r="G9" s="27"/>
@@ -18829,16 +18856,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="34" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="35">
         <v>10</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F10" s="35"/>
       <c r="G10" s="27"/>
@@ -18856,16 +18883,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="34" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="35">
         <v>600</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F11" s="35"/>
       <c r="G11" s="27"/>
@@ -18883,16 +18910,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="34" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="35">
         <v>20</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="27"/>
@@ -18910,16 +18937,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="34" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="35">
         <v>20</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F13" s="35"/>
       <c r="G13" s="27"/>
@@ -18937,16 +18964,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="34" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="35">
         <v>6</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F14" s="35"/>
       <c r="G14" s="27"/>
@@ -18964,16 +18991,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="34" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="35">
         <v>6</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F15" s="35"/>
       <c r="G15" s="27"/>
@@ -18994,7 +19021,7 @@
         <v>85</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D16" s="35">
         <v>4</v>
@@ -19018,16 +19045,16 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="24"/>
       <c r="B17" s="34" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D17" s="35">
         <v>20</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F17" s="35"/>
       <c r="G17" s="27"/>
@@ -19045,16 +19072,16 @@
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="24"/>
       <c r="B18" s="34" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D18" s="35">
         <v>7</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F18" s="35"/>
       <c r="G18" s="27"/>
@@ -19072,16 +19099,16 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="24"/>
       <c r="B19" s="34" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D19" s="35">
         <v>6</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F19" s="35"/>
       <c r="G19" s="27"/>
@@ -19099,16 +19126,16 @@
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="24"/>
       <c r="B20" s="34" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D20" s="35">
         <v>8</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F20" s="35"/>
       <c r="G20" s="27"/>
@@ -19458,12 +19485,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -19552,16 +19579,16 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="24"/>
       <c r="B6" s="34" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>40</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F6" s="35"/>
       <c r="G6" s="27"/>
@@ -19579,16 +19606,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="34" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="35">
         <v>30</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="27"/>
@@ -20014,12 +20041,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -20108,16 +20135,16 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="24"/>
       <c r="B6" s="34" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="35">
         <v>40</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F6" s="35"/>
       <c r="G6" s="27"/>
@@ -20135,16 +20162,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="34" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="35">
         <v>40</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="27"/>
@@ -20162,16 +20189,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="34" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="35">
         <v>40</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F8" s="35"/>
       <c r="G8" s="27"/>
@@ -20189,16 +20216,16 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="34" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="35">
         <v>80</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F9" s="35"/>
       <c r="G9" s="27"/>
@@ -20216,16 +20243,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="34" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="35">
         <v>6</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F10" s="35"/>
       <c r="G10" s="27"/>
@@ -20243,16 +20270,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="34" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="35">
         <v>800</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F11" s="35"/>
       <c r="G11" s="27"/>
@@ -20270,16 +20297,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="34" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="35">
         <v>8</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="27"/>
@@ -20297,16 +20324,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="34" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="35">
         <v>8</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="35"/>
       <c r="G13" s="27"/>
@@ -20324,16 +20351,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="34" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="35">
         <v>2</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F14" s="35"/>
       <c r="G14" s="27"/>
@@ -20351,16 +20378,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="34" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="35">
         <v>2</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F15" s="35"/>
       <c r="G15" s="27"/>
@@ -20378,16 +20405,16 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="24"/>
       <c r="B16" s="34" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D16" s="35">
         <v>20</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F16" s="35"/>
       <c r="G16" s="27"/>
@@ -20405,16 +20432,16 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="24"/>
       <c r="B17" s="34" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D17" s="35">
         <v>40</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F17" s="35"/>
       <c r="G17" s="27"/>
@@ -20432,16 +20459,16 @@
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="24"/>
       <c r="B18" s="34" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D18" s="35">
         <v>20</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F18" s="35"/>
       <c r="G18" s="27"/>
@@ -20459,16 +20486,16 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="24"/>
       <c r="B19" s="34" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D19" s="35">
         <v>6</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F19" s="35"/>
       <c r="G19" s="27"/>
@@ -20486,16 +20513,16 @@
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="24"/>
       <c r="B20" s="34" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D20" s="35">
         <v>20</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F20" s="35"/>
       <c r="G20" s="27"/>
@@ -20513,16 +20540,16 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="24"/>
       <c r="B21" s="34" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D21" s="35">
         <v>20</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F21" s="35"/>
       <c r="G21" s="27"/>
@@ -20540,16 +20567,16 @@
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="24"/>
       <c r="B22" s="34" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D22" s="35">
         <v>6</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F22" s="35"/>
       <c r="G22" s="27"/>
@@ -20567,16 +20594,16 @@
     <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="24"/>
       <c r="B23" s="34" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D23" s="35">
         <v>6</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F23" s="35"/>
       <c r="G23" s="27"/>
@@ -20597,7 +20624,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D24" s="35">
         <v>4</v>
@@ -20621,16 +20648,16 @@
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="24"/>
       <c r="B25" s="34" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D25" s="35">
         <v>100</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F25" s="35"/>
       <c r="G25" s="27"/>
@@ -20648,16 +20675,16 @@
     <row r="26" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="24"/>
       <c r="B26" s="34" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D26" s="35">
         <v>2</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F26" s="35"/>
       <c r="G26" s="27"/>
@@ -20675,16 +20702,16 @@
     <row r="27" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="24"/>
       <c r="B27" s="34" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D27" s="35">
         <v>4</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F27" s="35"/>
       <c r="G27" s="27"/>
@@ -20996,12 +21023,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -21093,13 +21120,13 @@
         <v>290</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="25">
         <v>40</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="27"/>
@@ -21117,16 +21144,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="25" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="25">
         <v>40</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="27"/>
@@ -21144,16 +21171,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="25" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="25">
         <v>64</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="27"/>
@@ -21171,16 +21198,16 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="25" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="25">
         <v>64</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="33"/>
@@ -21198,16 +21225,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="25">
         <v>6</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="33"/>
@@ -21225,16 +21252,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="25" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="25">
         <v>6</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="33"/>
@@ -21252,16 +21279,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="25">
         <v>6</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="33"/>
@@ -21279,16 +21306,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="25" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="25">
         <v>30</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="33"/>
@@ -21306,16 +21333,16 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="25" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="25">
         <v>6</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="33"/>
@@ -21333,16 +21360,16 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="25">
         <v>30</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="33"/>
@@ -21360,16 +21387,16 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D16" s="25">
         <v>40</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="33"/>
@@ -21387,16 +21414,16 @@
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="24"/>
       <c r="B17" s="25" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D17" s="25">
         <v>40</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="33"/>
@@ -21414,16 +21441,16 @@
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="24"/>
       <c r="B18" s="25" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D18" s="25">
         <v>1</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="33"/>
@@ -21441,16 +21468,16 @@
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="24"/>
       <c r="B19" s="25" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D19" s="25">
         <v>64</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="33"/>
@@ -21468,16 +21495,16 @@
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="24"/>
       <c r="B20" s="25" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D20" s="25">
         <v>64</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F20" s="26"/>
       <c r="G20" s="33"/>
@@ -21495,16 +21522,16 @@
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="24"/>
       <c r="B21" s="25" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D21" s="25">
         <v>20</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F21" s="26"/>
       <c r="G21" s="33"/>
@@ -21522,16 +21549,16 @@
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="24"/>
       <c r="B22" s="25" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D22" s="25">
         <v>20</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F22" s="26"/>
       <c r="G22" s="33"/>
@@ -21549,16 +21576,16 @@
     <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="24"/>
       <c r="B23" s="25" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D23" s="25">
         <v>64</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="33"/>
@@ -21576,16 +21603,16 @@
     <row r="24" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A24" s="24"/>
       <c r="B24" s="25" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D24" s="25">
         <v>20</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="33"/>
@@ -21603,16 +21630,16 @@
     <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="24"/>
       <c r="B25" s="25" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D25" s="25">
         <v>1</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F25" s="26"/>
       <c r="G25" s="33"/>
@@ -21633,7 +21660,7 @@
         <v>85</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D26" s="25">
         <v>30</v>
@@ -21970,12 +21997,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -22067,7 +22094,7 @@
         <v>252</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="52">
         <v>40</v>
@@ -22091,16 +22118,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="51" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="52">
         <v>40</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="27"/>
@@ -22118,16 +22145,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="51" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="52">
         <v>6</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="27"/>
@@ -22145,16 +22172,16 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="51" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="52">
         <v>40</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="33"/>
@@ -22172,7 +22199,7 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="51" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C10" s="51" t="s">
         <v>205</v>
@@ -22181,7 +22208,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="33"/>
@@ -22493,12 +22520,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -22590,10 +22617,10 @@
         <v>252</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E6" s="33" t="s">
         <v>254</v>
@@ -22607,16 +22634,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="33" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="33">
         <v>200</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="27"/>
@@ -22634,16 +22661,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="33" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="33">
         <v>40</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="27"/>
@@ -22661,10 +22688,10 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="33" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="33">
         <v>100</v>
@@ -22688,16 +22715,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="33" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="33">
         <v>300</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="33"/>
@@ -22715,16 +22742,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="33" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="33"/>
@@ -22735,16 +22762,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="33" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="33">
         <v>200</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="33"/>
@@ -22762,7 +22789,7 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="33" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>205</v>
@@ -22771,7 +22798,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="33"/>
@@ -22792,7 +22819,7 @@
         <v>85</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D14" s="33">
         <v>10</v>
@@ -23070,12 +23097,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -23164,16 +23191,16 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="24"/>
       <c r="B6" s="25" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D6" s="25">
         <v>40</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="27"/>
@@ -23191,16 +23218,16 @@
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
       <c r="B7" s="25" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D7" s="25">
         <v>40</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="27"/>
@@ -23218,16 +23245,16 @@
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="25" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" s="25">
         <v>40</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="27"/>
@@ -23245,16 +23272,16 @@
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="25" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D9" s="25">
         <v>40</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="33"/>
@@ -23272,16 +23299,16 @@
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D10" s="25">
         <v>500</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="33"/>
@@ -23299,16 +23326,16 @@
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D11" s="25">
         <v>10</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="33"/>
@@ -23326,16 +23353,16 @@
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D12" s="25">
         <v>10</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="33"/>
@@ -23353,16 +23380,16 @@
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="25" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D13" s="25">
         <v>6</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="33"/>
@@ -23380,7 +23407,7 @@
     <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="25" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>205</v>
@@ -23389,7 +23416,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="33"/>
@@ -23407,7 +23434,7 @@
     <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>205</v>
@@ -23416,7 +23443,7 @@
         <v>22</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="33"/>
@@ -23434,7 +23461,7 @@
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>205</v>
@@ -23443,7 +23470,7 @@
         <v>22</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="33"/>
@@ -23464,7 +23491,7 @@
         <v>85</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D17" s="25">
         <v>30</v>
@@ -23753,39 +23780,39 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -23794,61 +23821,61 @@
         <v>316</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -23856,7 +23883,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -23864,7 +23891,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
